--- a/stories/arbres/ATOM-SOC.TRA.001-03.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Papa et Inaya vont à l'aéroport. Inaya tient la main de papa. Ils restent avec un adulte. Papa, c'est l'adulte. Un avion roule. L'avion fait un grand souffle. Le sol vibre un peu. Papa dit : c'est un avion. C'est le nom du véhicule. Inaya répète : un avion. Ils regardent par la grande vitre. L'avion s'envole. Inaya entend le bruit. Plus tard, ils prennent le train de la ville. Le train fait tchou tchou. Papa dit : c'est un train. C'est un autre nom de véhicule. Inaya dit : un train. Elle reste avec papa. Sur le quai, une affiche montre l'eau. Un bateau glisse. Papa dit : c'est un bateau. Inaya dit : un bateau. Train, avion, bateau. Inaya nomme. Parce qu'elle est avec un adulte, elle voyage. Parce qu'elle a le nom du véhicule, elle peut le dire.</t>
+          <t>Papa et Inaya vont à l'aéroport. Inaya tient la main de papa. Ils restent avec un adulte. Papa, c'est l'adulte. Un avion roule. L'avion fait un grand souffle. Le sol vibre un peu. C'est un avion. C'est le nom du véhicule. Inaya répète : un avion. Ils regardent par la grande vitre. L'avion s'envole. Inaya entend le bruit. Plus tard, ils prennent le train de la ville. Le train fait tchou tchou. C'est un train. C'est un autre nom de véhicule. Un train. Elle reste avec papa. Sur le quai, une affiche montre l'eau. Un bateau glisse. C'est un bateau. Un bateau. Train, avion, bateau. Inaya nomme. Parce qu'elle est avec un adulte, elle voyage. Parce qu'elle a le nom du véhicule, elle peut le dire.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,19 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Papa et Inaya vont à l'aéroport. Inaya tient la main de papa. Ils restent avec un adulte. Papa, c'est l'adulte. Un avion roule. L'avion fait un grand souffle. Le sol vibre un peu.
+papa|C'est un avion. C'est le nom du véhicule.
+narrateur|Inaya répète : un avion. Ils regardent par la grande vitre. L'avion s'envole. Inaya entend le bruit. Plus tard, ils prennent le train de la ville. Le train fait tchou tchou.
+papa|C'est un train. C'est un autre nom de véhicule.
+enfant-f|Un train. Elle reste avec papa. Sur le quai, une affiche montre l'eau.
+narrateur|Un bateau glisse.
+papa|C'est un bateau.
+enfant-f|Un bateau. Train, avion, bateau.
+narrateur|Inaya nomme. Parce qu'elle est avec un adulte, elle voyage. Parce qu'elle a le nom du véhicule, elle peut le dire.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1498,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Inaya nomme un véhicule. Lequel ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Inaya a dit le nom du véhicule. Elle est restée avec un adulte. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1834,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Inaya s'assoit près de papa. Le train roule doucement.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2001,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.TRA.001-03.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.001-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1323,11 @@
 narrateur|Inaya nomme. Parce qu'elle est avec un adulte, elle voyage. Parce qu'elle a le nom du véhicule, elle peut le dire.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1505,6 +1515,7 @@
           <t>narrateur|Inaya nomme un véhicule. Lequel ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1687,7 @@
           <t>narrateur|Inaya a dit le nom du véhicule. Elle est restée avec un adulte. Papa est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1851,7 @@
           <t>narrateur|Inaya s'assoit près de papa. Le train roule doucement.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2062,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2277,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.TRA.001-03.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L'avion d'Inaya</t>
+          <t>L'avion derrière le nuage</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sarah veut voir l'avion depuis la terrasse. Un nuage le cache. Elle attend avec papa. L'avion reparaît, argenté.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Papa et Inaya vont à l'aéroport. Inaya tient la main de papa. Ils restent avec un adulte. Papa, c'est l'adulte. Un avion roule. L'avion fait un grand souffle. Le sol vibre un peu. C'est un avion. C'est le nom du véhicule. Inaya répète : un avion. Ils regardent par la grande vitre. L'avion s'envole. Inaya entend le bruit. Plus tard, ils prennent le train de la ville. Le train fait tchou tchou. C'est un train. C'est un autre nom de véhicule. Un train. Elle reste avec papa. Sur le quai, une affiche montre l'eau. Un bateau glisse. C'est un bateau. Un bateau. Train, avion, bateau. Inaya nomme. Parce qu'elle est avec un adulte, elle voyage. Parce qu'elle a le nom du véhicule, elle peut le dire.</t>
+          <t>Une feuille de géranium garde une goutte. La goutte brille sur le velours vert. Le fer de la rambarde est tiède. Un torchon blanc sèche sur le fil. Ça sent le café et la terre chaude. Sarah vit ici, avec papa. Tu as vu le torchon, Sarah ? Il danse un peu. Le vent le touche. En ce moment, Sarah lève les yeux. Le ciel est large et pâle. Papa, l'avion va passer ? Oui. On le regarde d'ici. Ils restent sur la terrasse. Sarah se tient près de papa. On reste avec un adulte. C'est plus simple. Un bruit monte, très loin. Le bruit devient un souffle. Je l'entends ! Oui. C'est un avion. C'est le nom du véhicule. Un avion. Un point argenté glisse entre les toits. Sarah pointe le ciel du doigt. Le voilà ! Un nuage gras passe devant. Le point argenté disparaît. Il est parti ? Il est derrière le nuage. On attend ici ? Oui. Sarah reste près de papa. Ses pieds restent sur les carreaux chauds. Une abeille visite le géranium. Tu restes avec moi ? Oui, papa. Dans la vallée, un train file tout petit. Tu entends le train ? Tchou tchou. Oui. C'est un train. Sarah écoute, sans bouger. Le nuage avance tout doucement.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa et Inaya vont à l'aéroport. Inaya tient la main de papa. Ils restent avec un adulte. Papa, c'est l'adulte. Un avion roule. L'avion fait un grand souffle. Le sol vibre un peu. Papa dit : c'est un avion. C'est le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt; du véhicule. Inaya répète : un avion. Ils regardent par la grande vitre. L'avion s'envole. Inaya entend le bruit. Plus tard, ils prennent le train de la ville. Le train fait tchou tchou. Papa dit : c'est un train. C'est un autre nom de véhicule. Inaya dit : un train. Elle reste avec papa. Sur le quai, une affiche montre l'eau. Un bateau glisse. Papa dit : c'est un bateau. Inaya dit : un bateau. Train, avion, bateau. Inaya nomme. Parce qu'elle est avec un adulte, elle voyage. Parce qu'elle a le nom du véhicule, elle peut le dire.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une feuille de géranium garde une goutte. La goutte brille sur le velours vert. Le fer de la rambarde est tiède. Un torchon blanc sèche sur le fil. Ça sent le café et la terre chaude. Sarah vit ici, avec papa. Tu as vu le torchon, Sarah ? Il danse un peu. Le vent le touche. En ce moment, Sarah lève les yeux. Le ciel est large et pâle. Papa, l'avion va passer ? Oui. On le regarde d'ici. Ils restent sur la terrasse. Sarah se tient près de papa. On reste avec un adulte. C'est plus simple. Un bruit monte, très loin. Le bruit devient un souffle. Je l'entends ! Oui. C'est un avion. C'est le nom du véhicule. Un avion. Un point argenté glisse entre les toits. Sarah pointe le ciel du doigt. Le voilà ! Un nuage gras passe devant. Le point argenté disparaît. Il est parti ? Il est derrière le nuage. On attend ici ? Oui. Sarah reste près de papa. Ses pieds restent sur les carreaux chauds. Une abeille visite le géranium. Tu restes avec moi ? Oui, papa. Dans la vallée, un train file tout petit. Tu entends le train ? Tchou tchou. Oui. C'est un train. Sarah écoute, sans bouger. Le nuage avance tout doucement.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,15 +1324,52 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Papa et Inaya vont à l'aéroport. Inaya tient la main de papa. Ils restent avec un adulte. Papa, c'est l'adulte. Un avion roule. L'avion fait un grand souffle. Le sol vibre un peu.
-papa|C'est un avion. C'est le nom du véhicule.
-narrateur|Inaya répète : un avion. Ils regardent par la grande vitre. L'avion s'envole. Inaya entend le bruit. Plus tard, ils prennent le train de la ville. Le train fait tchou tchou.
-papa|C'est un train. C'est un autre nom de véhicule.
-enfant-f|Un train. Elle reste avec papa. Sur le quai, une affiche montre l'eau.
-narrateur|Un bateau glisse.
-papa|C'est un bateau.
-enfant-f|Un bateau. Train, avion, bateau.
-narrateur|Inaya nomme. Parce qu'elle est avec un adulte, elle voyage. Parce qu'elle a le nom du véhicule, elle peut le dire.</t>
+          <t>narrateur|Une feuille de géranium garde une goutte.
+narrateur|La goutte brille sur le velours vert.
+narrateur|Le fer de la rambarde est tiède.
+narrateur|Un torchon blanc sèche sur le fil.
+narrateur|Ça sent le café et la terre chaude.
+narrateur|Sarah vit ici, avec papa.
+papa|Tu as vu le torchon, Sarah ?
+enfant-f|Il danse un peu.
+papa|Le vent le touche.
+narrateur|En ce moment, Sarah lève les yeux.
+narrateur|Le ciel est large et pâle.
+enfant-f|Papa, l'avion va passer ?
+papa|Oui.
+papa|On le regarde d'ici.
+narrateur|Ils restent sur la terrasse.
+narrateur|Sarah se tient près de papa.
+papa|On reste avec un adulte.
+papa|C'est plus simple.
+narrateur|Un bruit monte, très loin.
+narrateur|Le bruit devient un souffle.
+enfant-f|Je l'entends !
+papa|Oui.
+papa|C'est un avion.
+papa|C'est le nom du véhicule.
+enfant-f|Un avion.
+narrateur|Un point argenté glisse entre les toits.
+narrateur|Sarah pointe le ciel du doigt.
+enfant-f|Le voilà !
+narrateur|Un nuage gras passe devant.
+narrateur|Le point argenté disparaît.
+enfant-f|Il est parti ?
+papa|Il est derrière le nuage.
+papa|On attend ici ?
+enfant-f|Oui.
+narrateur|Sarah reste près de papa.
+narrateur|Ses pieds restent sur les carreaux chauds.
+narrateur|Une abeille visite le géranium.
+papa|Tu restes avec moi ?
+enfant-f|Oui, papa.
+narrateur|Dans la vallée, un train file tout petit.
+papa|Tu entends le train ?
+enfant-f|Tchou tchou.
+papa|Oui.
+papa|C'est un train.
+narrateur|Sarah écoute, sans bouger.
+narrateur|Le nuage avance tout doucement.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1352,12 +1401,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Inaya nomme un véhicule. Lequel ?</t>
+          <t>Sarah nomme le véhicule du ciel. Lequel ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Inaya &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;me un véhicule. Lequel ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah nomme le véhicule du ciel. Lequel ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1372,7 +1421,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>avion | train | bateau | un avion | le train</t>
+          <t>avion | un avion | l'avion | train | bateau</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1387,7 +1436,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle dit le nom du véhicule. Avion, train ou bateau ?</t>
+          <t>Elle a vu un avion. Quel véhicule ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1436,7 +1485,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1512,10 +1561,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Inaya nomme un véhicule. Lequel ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Sarah nomme le véhicule du ciel.
+narrateur|Lequel ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1540,12 +1589,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Inaya a dit le nom du véhicule. Elle est restée avec un adulte. Papa est là.</t>
+          <t>Le nuage s'étire, puis se fend. Un éclat d'argent revient. L'avion ! Oui. Tu as dit le nom. Bravo. Sarah lève la main. Elle salue le point brillant. L'avion trace un trait blanc. On reste sur la terrasse ? Oui. Sarah se colle un peu à papa. Le souffle s'éloigne. Sur la table, une soucoupe d'eau attend. Un bateau de papier y flotte. Et ça, c'est un bateau. Un bateau. Sarah souffle tout doux. La voile de papier penche.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Inaya a dit le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt; du véhicule. Elle est restée avec un adulte. Papa est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le nuage s'étire, puis se fend. Un éclat d'argent revient. L'avion ! Oui. Tu as dit le nom. Bravo. Sarah lève la main. Elle salue le point brillant. L'avion trace un trait blanc. On reste sur la terrasse ? Oui. Sarah se colle un peu à papa. Le souffle s'éloigne. Sur la table, une soucoupe d'eau attend. Un bateau de papier y flotte. Et ça, c'est un bateau. Un bateau. Sarah souffle tout doux. La voile de papier penche.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1608,7 +1657,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1684,10 +1733,27 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Inaya a dit le nom du véhicule. Elle est restée avec un adulte. Papa est là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le nuage s'étire, puis se fend.
+narrateur|Un éclat d'argent revient.
+enfant-f|L'avion !
+papa|Oui.
+papa|Tu as dit le nom.
+papa|Bravo.
+narrateur|Sarah lève la main.
+narrateur|Elle salue le point brillant.
+narrateur|L'avion trace un trait blanc.
+papa|On reste sur la terrasse ?
+enfant-f|Oui.
+narrateur|Sarah se colle un peu à papa.
+narrateur|Le souffle s'éloigne.
+narrateur|Sur la table, une soucoupe d'eau attend.
+narrateur|Un bateau de papier y flotte.
+papa|Et ça, c'est un bateau.
+enfant-f|Un bateau.
+narrateur|Sarah souffle tout doux.
+narrateur|La voile de papier penche.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1712,12 +1778,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Inaya s'assoit près de papa. Le train roule doucement.</t>
+          <t>L'avion devient un grain de riz. Sarah le suit encore des yeux. Il est tout petit. Il va loin. Nous, on reste ici. Le torchon s'est arrêté de danser. La goutte a quitté la feuille. Une tache sombre reste sur le velours. Tu as vu l'avion ? Oui. Derrière le nuage, puis après. Merci d'avoir attendu. Sarah pose le doigt sur la rambarde. Le fer est encore tiède.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Inaya s'assoit près de papa. Le train roule doucement.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'avion devient un grain de riz. Sarah le suit encore des yeux. Il est tout petit. Il va loin. Nous, on reste ici. Le torchon s'est arrêté de danser. La goutte a quitté la feuille. Une tache sombre reste sur le velours. Tu as vu l'avion ? Oui. Derrière le nuage, puis après. Merci d'avoir attendu. Sarah pose le doigt sur la rambarde. Le fer est encore tiède.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1780,7 +1846,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1848,10 +1914,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Inaya s'assoit près de papa. Le train roule doucement.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|L'avion devient un grain de riz.
+narrateur|Sarah le suit encore des yeux.
+enfant-f|Il est tout petit.
+papa|Il va loin.
+papa|Nous, on reste ici.
+narrateur|Le torchon s'est arrêté de danser.
+narrateur|La goutte a quitté la feuille.
+narrateur|Une tache sombre reste sur le velours.
+papa|Tu as vu l'avion ?
+enfant-f|Oui.
+enfant-f|Derrière le nuage, puis après.
+papa|Merci d'avoir attendu.
+narrateur|Sarah pose le doigt sur la rambarde.
+narrateur|Le fer est encore tiède.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1876,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le ciel redevient large et pâle. L'avion est passé. Oui. Le géranium sent encore la terre. La rambarde garde la chaleur du jour.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le ciel redevient large et pâle. L'avion est passé. Oui. Le géranium sent encore la terre. La rambarde garde la chaleur du jour.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1937,14 +2015,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2016,10 +2094,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le ciel redevient large et pâle.
+enfant-f|L'avion est passé.
+papa|Oui.
+narrateur|Le géranium sent encore la terre.
+narrateur|La rambarde garde la chaleur du jour.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2038,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2076,6 +2157,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.TRA.001-03.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.001-03.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>aéroport</t>
+          <t>terrasse d'immeuble, fin d'après-midi</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Inaya, papa</t>
+          <t>Sarah, papa</t>
         </is>
       </c>
     </row>
